--- a/MainTop/26.05.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/26.05.2026 Таня ВБ/print_print_sorted.xlsx
@@ -5,22 +5,33 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\26.05.2026 Таня ВБ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\26.05.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED1C332-6AD5-4466-A1CD-8E8A74C0481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7328345-C5B1-40C0-ACDF-2FC129613906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="125">
   <si>
     <t>Артикул</t>
   </si>
@@ -392,13 +403,16 @@
   </si>
   <si>
     <t>6_а5_настройки_60</t>
+  </si>
+  <si>
+    <t>на 4 города</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,6 +424,15 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -450,7 +473,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -473,11 +496,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -487,6 +521,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -789,13 +826,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="5" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,8 +865,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -852,8 +897,12 @@
       <c r="I2" s="2">
         <v>0.79999999999999716</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="8">
+        <f>F2/4</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -881,8 +930,12 @@
       <c r="I3" s="2">
         <v>-17.8</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="8">
+        <f t="shared" ref="J3:J66" si="0">F3/4</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -910,8 +963,12 @@
       <c r="I4" s="2">
         <v>-9</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -939,8 +996,12 @@
       <c r="I5" s="2">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -968,8 +1029,12 @@
       <c r="I6" s="2">
         <v>10.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -997,8 +1062,12 @@
       <c r="I7" s="2">
         <v>15.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1026,8 +1095,12 @@
       <c r="I8" s="2">
         <v>-12.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1055,8 +1128,12 @@
       <c r="I9" s="2">
         <v>-66.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1084,8 +1161,12 @@
       <c r="I10" s="2">
         <v>-39.9</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1113,8 +1194,12 @@
       <c r="I11" s="2">
         <v>-2.399999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1142,8 +1227,12 @@
       <c r="I12" s="2">
         <v>-6.6000000000000014</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -1171,8 +1260,12 @@
       <c r="I13" s="2">
         <v>-42.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -1200,8 +1293,12 @@
       <c r="I14" s="2">
         <v>-12.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1229,8 +1326,12 @@
       <c r="I15" s="2">
         <v>-7.8999999999999986</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -1258,8 +1359,12 @@
       <c r="I16" s="3">
         <v>-4.6000000000000014</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
@@ -1287,8 +1392,12 @@
       <c r="I17" s="3">
         <v>0.69999999999999929</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1316,8 +1425,12 @@
       <c r="I18" s="3">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -1345,8 +1458,12 @@
       <c r="I19" s="3">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
@@ -1374,8 +1491,12 @@
       <c r="I20" s="3">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
@@ -1403,8 +1524,12 @@
       <c r="I21" s="3">
         <v>0.90000000000000036</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
@@ -1432,8 +1557,12 @@
       <c r="I22" s="3">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
@@ -1461,8 +1590,12 @@
       <c r="I23" s="3">
         <v>-31.7</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
@@ -1490,8 +1623,12 @@
       <c r="I24" s="3">
         <v>-17.100000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>34</v>
       </c>
@@ -1519,8 +1656,12 @@
       <c r="I25" s="3">
         <v>-23.7</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
@@ -1548,8 +1689,12 @@
       <c r="I26" s="3">
         <v>-2.6999999999999988</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>36</v>
       </c>
@@ -1577,8 +1722,12 @@
       <c r="I27" s="3">
         <v>-3.8000000000000012</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
@@ -1606,8 +1755,12 @@
       <c r="I28" s="3">
         <v>-5.1999999999999993</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
@@ -1635,8 +1788,12 @@
       <c r="I29" s="3">
         <v>-5.0999999999999996</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
@@ -1664,8 +1821,12 @@
       <c r="I30" s="3">
         <v>-2.6999999999999988</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
@@ -1693,8 +1854,12 @@
       <c r="I31" s="3">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
@@ -1722,8 +1887,12 @@
       <c r="I32" s="3">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
@@ -1751,8 +1920,12 @@
       <c r="I33" s="3">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
@@ -1780,8 +1953,12 @@
       <c r="I34" s="3">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>44</v>
       </c>
@@ -1809,8 +1986,12 @@
       <c r="I35" s="3">
         <v>-2.6</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>45</v>
       </c>
@@ -1838,8 +2019,12 @@
       <c r="I36" s="3">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -1867,8 +2052,12 @@
       <c r="I37" s="3">
         <v>-1.6999999999999991</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>47</v>
       </c>
@@ -1896,8 +2085,12 @@
       <c r="I38" s="3">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>48</v>
       </c>
@@ -1925,8 +2118,12 @@
       <c r="I39" s="3">
         <v>-36.200000000000003</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>49</v>
       </c>
@@ -1954,8 +2151,12 @@
       <c r="I40" s="3">
         <v>-18.399999999999999</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J40" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>50</v>
       </c>
@@ -1983,8 +2184,12 @@
       <c r="I41" s="3">
         <v>-17.3</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J41" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>51</v>
       </c>
@@ -2012,8 +2217,12 @@
       <c r="I42" s="3">
         <v>-17.399999999999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J42" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>52</v>
       </c>
@@ -2041,8 +2250,12 @@
       <c r="I43" s="3">
         <v>-17.5</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>53</v>
       </c>
@@ -2070,8 +2283,12 @@
       <c r="I44" s="3">
         <v>-16.5</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>54</v>
       </c>
@@ -2099,8 +2316,12 @@
       <c r="I45" s="3">
         <v>-16.399999999999999</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J45" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>55</v>
       </c>
@@ -2128,8 +2349,12 @@
       <c r="I46" s="3">
         <v>-14.2</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>56</v>
       </c>
@@ -2157,8 +2382,12 @@
       <c r="I47" s="3">
         <v>-12.9</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J47" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>57</v>
       </c>
@@ -2186,8 +2415,12 @@
       <c r="I48" s="3">
         <v>-8.6999999999999993</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J48" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>58</v>
       </c>
@@ -2215,8 +2448,12 @@
       <c r="I49" s="3">
         <v>-10.9</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>59</v>
       </c>
@@ -2244,8 +2481,12 @@
       <c r="I50" s="3">
         <v>-7.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>60</v>
       </c>
@@ -2273,8 +2514,12 @@
       <c r="I51" s="3">
         <v>-9.6</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>61</v>
       </c>
@@ -2302,8 +2547,12 @@
       <c r="I52" s="3">
         <v>-10.7</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J52" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>62</v>
       </c>
@@ -2331,8 +2580,12 @@
       <c r="I53" s="3">
         <v>-9.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J53" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>63</v>
       </c>
@@ -2360,8 +2613,12 @@
       <c r="I54" s="3">
         <v>-8.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J54" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>64</v>
       </c>
@@ -2389,8 +2646,12 @@
       <c r="I55" s="3">
         <v>-8.6</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>65</v>
       </c>
@@ -2418,8 +2679,12 @@
       <c r="I56" s="3">
         <v>-7.5</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>66</v>
       </c>
@@ -2447,8 +2712,12 @@
       <c r="I57" s="3">
         <v>-8.4</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>67</v>
       </c>
@@ -2476,8 +2745,12 @@
       <c r="I58" s="3">
         <v>-5.4</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>68</v>
       </c>
@@ -2505,8 +2778,12 @@
       <c r="I59" s="3">
         <v>-7.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J59" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>69</v>
       </c>
@@ -2534,8 +2811,12 @@
       <c r="I60" s="3">
         <v>-5.3000000000000007</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J60" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>70</v>
       </c>
@@ -2563,8 +2844,12 @@
       <c r="I61" s="3">
         <v>-6.1999999999999993</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J61" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>71</v>
       </c>
@@ -2592,8 +2877,12 @@
       <c r="I62" s="3">
         <v>-6.1999999999999993</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J62" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>72</v>
       </c>
@@ -2621,8 +2910,12 @@
       <c r="I63" s="3">
         <v>-5.0999999999999996</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J63" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>73</v>
       </c>
@@ -2650,8 +2943,12 @@
       <c r="I64" s="3">
         <v>-5.3000000000000007</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J64" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>74</v>
       </c>
@@ -2679,8 +2976,12 @@
       <c r="I65" s="3">
         <v>-5.1999999999999993</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J65" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>75</v>
       </c>
@@ -2708,8 +3009,12 @@
       <c r="I66" s="3">
         <v>-5.1999999999999993</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J66" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>76</v>
       </c>
@@ -2737,8 +3042,12 @@
       <c r="I67" s="3">
         <v>-5.1999999999999993</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J67" s="8">
+        <f t="shared" ref="J67:J111" si="1">F67/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>77</v>
       </c>
@@ -2766,8 +3075,12 @@
       <c r="I68" s="4">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J68" s="8">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>79</v>
       </c>
@@ -2795,8 +3108,12 @@
       <c r="I69" s="4">
         <v>16</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J69" s="8">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>80</v>
       </c>
@@ -2824,8 +3141,12 @@
       <c r="I70" s="4">
         <v>16.3</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J70" s="8">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>81</v>
       </c>
@@ -2853,8 +3174,12 @@
       <c r="I71" s="4">
         <v>10.3</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J71" s="8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>82</v>
       </c>
@@ -2882,8 +3207,12 @@
       <c r="I72" s="4">
         <v>-0.30000000000000071</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J72" s="8">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>83</v>
       </c>
@@ -2911,8 +3240,12 @@
       <c r="I73" s="4">
         <v>3.3000000000000012</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J73" s="8">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>84</v>
       </c>
@@ -2940,8 +3273,12 @@
       <c r="I74" s="4">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J74" s="8">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>85</v>
       </c>
@@ -2969,8 +3306,12 @@
       <c r="I75" s="4">
         <v>-7</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J75" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>86</v>
       </c>
@@ -2998,8 +3339,12 @@
       <c r="I76" s="4">
         <v>-8.1000000000000014</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J76" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>87</v>
       </c>
@@ -3027,8 +3372,12 @@
       <c r="I77" s="4">
         <v>-10.5</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J77" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>88</v>
       </c>
@@ -3056,8 +3405,12 @@
       <c r="I78" s="4">
         <v>-0.30000000000000071</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J78" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>89</v>
       </c>
@@ -3085,8 +3438,12 @@
       <c r="I79" s="4">
         <v>-3.6999999999999988</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J79" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>90</v>
       </c>
@@ -3114,8 +3471,12 @@
       <c r="I80" s="4">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J80" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>91</v>
       </c>
@@ -3143,8 +3504,12 @@
       <c r="I81" s="4">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J81" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>92</v>
       </c>
@@ -3172,8 +3537,12 @@
       <c r="I82" s="4">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J82" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>93</v>
       </c>
@@ -3201,8 +3570,12 @@
       <c r="I83" s="4">
         <v>-9.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J83" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>94</v>
       </c>
@@ -3230,8 +3603,12 @@
       <c r="I84" s="4">
         <v>-6.1</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J84" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>95</v>
       </c>
@@ -3259,8 +3636,12 @@
       <c r="I85" s="4">
         <v>-1.8000000000000009</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J85" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>96</v>
       </c>
@@ -3288,8 +3669,12 @@
       <c r="I86" s="4">
         <v>-1.6999999999999991</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J86" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>97</v>
       </c>
@@ -3317,8 +3702,12 @@
       <c r="I87" s="4">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J87" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>98</v>
       </c>
@@ -3346,8 +3735,12 @@
       <c r="I88" s="4">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J88" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>99</v>
       </c>
@@ -3375,8 +3768,12 @@
       <c r="I89" s="4">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J89" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>100</v>
       </c>
@@ -3404,8 +3801,12 @@
       <c r="I90" s="4">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J90" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>101</v>
       </c>
@@ -3433,8 +3834,12 @@
       <c r="I91" s="4">
         <v>-1.6999999999999991</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J91" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>102</v>
       </c>
@@ -3462,8 +3867,12 @@
       <c r="I92" s="4">
         <v>-1.6</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J92" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>103</v>
       </c>
@@ -3491,8 +3900,12 @@
       <c r="I93" s="4">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J93" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>104</v>
       </c>
@@ -3520,8 +3933,12 @@
       <c r="I94" s="4">
         <v>-43.2</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J94" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>105</v>
       </c>
@@ -3549,8 +3966,12 @@
       <c r="I95" s="5">
         <v>-11</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J95" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>106</v>
       </c>
@@ -3578,8 +3999,12 @@
       <c r="I96" s="5">
         <v>-8.6999999999999993</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J96" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>107</v>
       </c>
@@ -3607,8 +4032,12 @@
       <c r="I97" s="5">
         <v>-10.7</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J97" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>108</v>
       </c>
@@ -3636,8 +4065,12 @@
       <c r="I98" s="5">
         <v>-6.5</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J98" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>109</v>
       </c>
@@ -3665,8 +4098,12 @@
       <c r="I99" s="5">
         <v>-12.9</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J99" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>110</v>
       </c>
@@ -3694,8 +4131,12 @@
       <c r="I100" s="5">
         <v>-8.6999999999999993</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J100" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>111</v>
       </c>
@@ -3723,8 +4164,12 @@
       <c r="I101" s="5">
         <v>-10.6</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J101" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>112</v>
       </c>
@@ -3752,8 +4197,12 @@
       <c r="I102" s="5">
         <v>-9.5</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J102" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>113</v>
       </c>
@@ -3781,8 +4230,12 @@
       <c r="I103" s="5">
         <v>-7.5</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J103" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>114</v>
       </c>
@@ -3810,8 +4263,12 @@
       <c r="I104" s="5">
         <v>-7.5</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J104" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>115</v>
       </c>
@@ -3839,8 +4296,12 @@
       <c r="I105" s="5">
         <v>-5.4</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J105" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>116</v>
       </c>
@@ -3868,8 +4329,12 @@
       <c r="I106" s="5">
         <v>-6.4</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J106" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>117</v>
       </c>
@@ -3897,8 +4362,12 @@
       <c r="I107" s="6">
         <v>-3.9</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J107" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>119</v>
       </c>
@@ -3926,8 +4395,12 @@
       <c r="I108" s="6">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J108" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>120</v>
       </c>
@@ -3955,8 +4428,12 @@
       <c r="I109" s="6">
         <v>-6.4</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J109" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>121</v>
       </c>
@@ -3984,8 +4461,12 @@
       <c r="I110" s="6">
         <v>-5.0999999999999996</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J110" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>122</v>
       </c>
@@ -4013,8 +4494,19 @@
       <c r="I111" s="6">
         <v>-8.4</v>
       </c>
+      <c r="J111" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J112" s="9">
+        <f>SUM(J2:J111)</f>
+        <v>275</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>